--- a/Documentation/JavaScript_Roadmap_Checklist.xlsx
+++ b/Documentation/JavaScript_Roadmap_Checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anike\Desktop\AdvanceJS\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C45FCE8-4E3B-492C-B50B-60FB371E6089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40DA2F96-9E69-4BDF-B976-1844D5A972B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
@@ -187,7 +187,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,6 +200,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -209,7 +217,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -217,13 +225,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,159 +574,159 @@
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="1" max="1" width="27.21875" customWidth="1"/>
+    <col min="2" max="2" width="18" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B14" t="s">
-        <v>16</v>
+      <c r="B14" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B15" t="s">
-        <v>16</v>
+      <c r="B15" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" t="s">
-        <v>16</v>
+      <c r="B16" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" t="s">
-        <v>16</v>
+      <c r="B17" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="4" t="s">
         <v>3</v>
       </c>
     </row>
@@ -695,135 +740,135 @@
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="18" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
-        <v>16</v>
+      <c r="B2" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
-        <v>16</v>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B11" t="s">
-        <v>16</v>
+      <c r="B11" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
+      <c r="B12" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -837,143 +882,143 @@
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
     </row>

--- a/Documentation/JavaScript_Roadmap_Checklist.xlsx
+++ b/Documentation/JavaScript_Roadmap_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anike\Desktop\AdvanceJS\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40DA2F96-9E69-4BDF-B976-1844D5A972B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514A6824-7E27-4849-B9D0-445CA6EF1B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -244,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -269,6 +269,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -741,134 +751,134 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="11" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="11" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>16</v>
+      <c r="B4" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>16</v>
+      <c r="B5" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>16</v>
+      <c r="B6" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>16</v>
+      <c r="B7" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>16</v>
+      <c r="B8" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>16</v>
+      <c r="B9" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>16</v>
+      <c r="B10" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="11" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="11" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="11" t="s">
         <v>16</v>
       </c>
     </row>

--- a/Documentation/JavaScript_Roadmap_Checklist.xlsx
+++ b/Documentation/JavaScript_Roadmap_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anike\Desktop\AdvanceJS\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514A6824-7E27-4849-B9D0-445CA6EF1B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D1CAF1-894C-4BB2-95EA-65539C225037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -275,10 +275,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -750,15 +752,15 @@
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18" style="13" customWidth="1"/>
+    <col min="1" max="1" width="18" style="13" customWidth="1"/>
+    <col min="2" max="2" width="18" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -766,7 +768,7 @@
       <c r="A2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -774,7 +776,7 @@
       <c r="A3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -782,7 +784,7 @@
       <c r="A4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -790,7 +792,7 @@
       <c r="A5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -798,7 +800,7 @@
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -806,7 +808,7 @@
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -814,7 +816,7 @@
       <c r="A8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -822,7 +824,7 @@
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -830,7 +832,7 @@
       <c r="A10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -838,7 +840,7 @@
       <c r="A11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -846,7 +848,7 @@
       <c r="A12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -854,23 +856,23 @@
       <c r="A13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>16</v>
+      <c r="B13" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>16</v>
+      <c r="B14" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>16</v>
       </c>
     </row>
@@ -878,7 +880,7 @@
       <c r="A16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="12" t="s">
         <v>16</v>
       </c>
     </row>

--- a/Documentation/JavaScript_Roadmap_Checklist.xlsx
+++ b/Documentation/JavaScript_Roadmap_Checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anike\Desktop\AdvanceJS\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D1CAF1-894C-4BB2-95EA-65539C225037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98CD671-886C-45D1-A62B-E67CC0CDB452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
@@ -187,18 +187,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -244,12 +239,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -258,18 +253,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -752,135 +739,135 @@
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" style="13" customWidth="1"/>
-    <col min="2" max="2" width="18" style="9" customWidth="1"/>
+    <col min="1" max="1" width="18" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -895,142 +882,142 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.5546875" customWidth="1"/>
-    <col min="2" max="2" width="18" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>16</v>
+      <c r="B2" s="7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>16</v>
+      <c r="B3" s="7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>16</v>
+      <c r="B4" s="7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>16</v>
       </c>
     </row>

--- a/Documentation/JavaScript_Roadmap_Checklist.xlsx
+++ b/Documentation/JavaScript_Roadmap_Checklist.xlsx
@@ -1,28 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anike\Desktop\AdvanceJS\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98CD671-886C-45D1-A62B-E67CC0CDB452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C219EE-50AE-406A-AB80-02254EBD342C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
-    <sheet name="Intermediate" sheetId="2" r:id="rId2"/>
-    <sheet name="Advanced" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="55">
   <si>
     <t>Topic</t>
   </si>
@@ -30,9 +28,6 @@
     <t>Learned (☑/☐)</t>
   </si>
   <si>
-    <t>Variables</t>
-  </si>
-  <si>
     <t>☑</t>
   </si>
   <si>
@@ -181,13 +176,22 @@
   </si>
   <si>
     <t>Web APIs</t>
+  </si>
+  <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
+    <t>Advance</t>
+  </si>
+  <si>
+    <t>Basic</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -198,6 +202,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -239,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -253,20 +265,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -570,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.21875" customWidth="1"/>
@@ -585,443 +585,426 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>3</v>
-      </c>
+    <row r="2" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="5"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="5"/>
+    </row>
+    <row r="22" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>3</v>
+      <c r="B23" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="5"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18" style="9" customWidth="1"/>
-    <col min="2" max="2" width="18" style="5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.5546875" customWidth="1"/>
-    <col min="2" max="2" width="18" style="5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A38:B39"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="A2:B3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Documentation/JavaScript_Roadmap_Checklist.xlsx
+++ b/Documentation/JavaScript_Roadmap_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anike\Desktop\AdvanceJS\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C219EE-50AE-406A-AB80-02254EBD342C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64254A85-ECED-4116-9455-5B0E32976F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Documentation/JavaScript_Roadmap_Checklist.xlsx
+++ b/Documentation/JavaScript_Roadmap_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anike\Desktop\AdvanceJS\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64254A85-ECED-4116-9455-5B0E32976F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30369994-707A-42A7-A945-C980D6A39226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -251,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -267,6 +267,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -896,27 +902,27 @@
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>15</v>
+      <c r="B43" s="7" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>15</v>
+      <c r="B44" s="7" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>15</v>
+      <c r="B45" s="7" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
